--- a/food_beverage_order_forms/041_event_menu_preferences_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/041_event_menu_preferences_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1178,8 +1178,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'gluten_free'}</t>
+          <t>gluten_free</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Gluten Free'}</t>
+          <t>Gluten Free</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'low-fat'}</t>
+          <t>low-fat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Low-Fat'}</t>
+          <t>Low-Fat</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'party'}</t>
+          <t>party</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Party'}</t>
+          <t>Party</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
